--- a/ThinkITAM/Resources/Template/UserInfoTemplate.xlsx
+++ b/ThinkITAM/Resources/Template/UserInfoTemplate.xlsx
@@ -1,30 +1,24 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="27932"/>
-  <workbookPr defaultThemeVersion="202300"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="24334"/>
+  <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\yaobu\Desktop\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\YAOBUS\Desktop\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:9_{F60895D9-A379-4DD7-8F33-6F66BCECE983}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{4E325443-5AF9-4CE2-9136-49E1800673D1}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="17565" yWindow="0" windowWidth="26010" windowHeight="20985" xr2:uid="{070EF696-D8B0-4554-9C49-E41C26B09585}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15840" xr2:uid="{070EF696-D8B0-4554-9C49-E41C26B09585}"/>
   </bookViews>
   <sheets>
     <sheet name="UserInfo" sheetId="1" r:id="rId1"/>
   </sheets>
   <calcPr calcId="114210"/>
   <extLst>
-    <ext xmlns:xcalcf="http://schemas.microsoft.com/office/spreadsheetml/2018/calcfeatures" uri="{B58B0392-4F1F-4190-BB64-5DF3571DCE5F}">
-      <xcalcf:calcFeatures>
-        <xcalcf:feature name="microsoft.com:RD"/>
-        <xcalcf:feature name="microsoft.com:FV"/>
-        <xcalcf:feature name="microsoft.com:LET_WF"/>
-        <xcalcf:feature name="microsoft.com:LAMBDA_WF"/>
-        <xcalcf:feature name="microsoft.com:ARRAYTEXT_WF"/>
-      </xcalcf:calcFeatures>
+    <ext xmlns:xlwcv="http://schemas.microsoft.com/office/spreadsheetml/2024/workbookCompatibilityVersion" uri="{D14903EA-33C4-47F7-8F05-3474C54BE107}">
+      <xlwcv:version setVersion="1"/>
     </ext>
   </extLst>
 </workbook>
@@ -155,9 +149,6 @@
     <t>Department</t>
   </si>
   <si>
-    <t>UserGroup</t>
-  </si>
-  <si>
     <t>Phone</t>
   </si>
   <si>
@@ -165,13 +156,17 @@
   </si>
   <si>
     <t>UserUnit</t>
+  </si>
+  <si>
+    <t>UserGroups</t>
+    <phoneticPr fontId="0" type="noConversion"/>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="3" x14ac:knownFonts="1">
+  <fonts count="4" x14ac:knownFonts="1">
     <font>
       <sz val="10"/>
       <name val="Arial"/>
@@ -190,6 +185,11 @@
       <name val="宋体"/>
       <family val="3"/>
       <charset val="134"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <name val="Arial"/>
+      <family val="2"/>
     </font>
   </fonts>
   <fills count="2">
@@ -212,8 +212,9 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="1">
+  <cellXfs count="2">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="常规" xfId="0" builtinId="0"/>
@@ -569,17 +570,17 @@
       <c r="C1" t="s">
         <v>2</v>
       </c>
-      <c r="D1" t="s">
+      <c r="D1" s="1" t="s">
+        <v>6</v>
+      </c>
+      <c r="E1" t="s">
+        <v>5</v>
+      </c>
+      <c r="F1" t="s">
         <v>3</v>
       </c>
-      <c r="E1" t="s">
-        <v>6</v>
-      </c>
-      <c r="F1" t="s">
+      <c r="G1" t="s">
         <v>4</v>
-      </c>
-      <c r="G1" t="s">
-        <v>5</v>
       </c>
     </row>
   </sheetData>
